--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tom.huang\Desktop\page\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\page\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3A67FB-B246-4E22-B8D9-2A7430EC6B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADC5BD0-91B4-49F0-854E-D535415F0BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="4" r:id="rId1"/>
@@ -353,10 +353,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Processor Brand</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Brand Model Name</t>
   </si>
   <si>
@@ -730,6 +726,9 @@
   <si>
     <t>140W</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Silicon Brand</t>
   </si>
 </sst>
 </file>
@@ -737,28 +736,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="165" formatCode="0_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -766,13 +765,13 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="新細明體"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -806,7 +805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -818,7 +817,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1201,10 +1200,10 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1267,7 +1266,7 @@
         <v>9</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>13</v>
@@ -1308,7 +1307,7 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>57</v>
@@ -1415,7 +1414,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>57</v>
@@ -1522,7 +1521,7 @@
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>57</v>
@@ -1629,7 +1628,7 @@
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>57</v>
@@ -1736,13 +1735,13 @@
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D6" s="1">
         <v>82</v>
@@ -1843,13 +1842,13 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D7" s="1">
         <v>82</v>
@@ -1950,7 +1949,7 @@
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>64</v>
@@ -2057,7 +2056,7 @@
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>64</v>
@@ -2164,7 +2163,7 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>57</v>
@@ -2378,13 +2377,13 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
@@ -2426,7 +2425,7 @@
         <v>500</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>46</v>
@@ -2465,7 +2464,7 @@
         <v>2</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE12" s="1">
         <v>99</v>
@@ -2474,7 +2473,7 @@
         <v>210</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH12" s="1">
         <v>19.899999999999999</v>
@@ -2485,7 +2484,7 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
@@ -2530,13 +2529,13 @@
         <v>240</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>30</v>
@@ -2551,7 +2550,7 @@
         <v>48</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X13" s="1" t="s">
         <v>50</v>
@@ -2572,7 +2571,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AE13" s="1">
         <v>84</v>
@@ -2581,10 +2580,10 @@
         <v>245</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AI13" s="1">
         <v>2</v>
@@ -2592,7 +2591,7 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>64</v>
@@ -2640,7 +2639,7 @@
         <v>500</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>46</v>
@@ -2688,10 +2687,10 @@
         <v>280</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AI14" s="1">
         <v>3</v>
@@ -2699,13 +2698,13 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="D15" s="1">
         <v>140</v>
@@ -2747,10 +2746,10 @@
         <v>500</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>30</v>
@@ -2786,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE15" s="1">
         <v>80</v>
@@ -2795,7 +2794,7 @@
         <v>250</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AH15" s="1">
         <v>24.8</v>
@@ -2806,13 +2805,13 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
@@ -2854,10 +2853,10 @@
         <v>500</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>30</v>
@@ -2875,10 +2874,10 @@
         <v>1</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z16" s="1" t="s">
         <v>30</v>
@@ -2893,7 +2892,7 @@
         <v>2</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE16" s="1">
         <v>90</v>
@@ -2902,10 +2901,10 @@
         <v>240</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AI16" s="1">
         <v>2.5</v>
@@ -2913,7 +2912,7 @@
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>57</v>
@@ -2961,7 +2960,7 @@
         <v>500</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>46</v>
@@ -3000,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE17" s="1">
         <v>80</v>
@@ -3009,7 +3008,7 @@
         <v>250</v>
       </c>
       <c r="AG17" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AH17" s="1">
         <v>25.6</v>
@@ -3020,7 +3019,7 @@
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>57</v>
@@ -3035,13 +3034,13 @@
         <v>140</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>30</v>
@@ -3068,7 +3067,7 @@
         <v>500</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>46</v>
@@ -3116,7 +3115,7 @@
         <v>330</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AH18" s="1">
         <v>22.9</v>
@@ -3127,13 +3126,13 @@
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="D19" s="1">
         <v>80</v>
@@ -3148,7 +3147,7 @@
         <v>59</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="1">
         <v>50</v>
@@ -3175,10 +3174,10 @@
         <v>400</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>29</v>
@@ -3193,7 +3192,7 @@
         <v>48</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X19" s="1" t="s">
         <v>31</v>
@@ -3223,10 +3222,10 @@
         <v>200</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AI19" s="1">
         <v>1.46</v>
@@ -3234,7 +3233,7 @@
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>57</v>
@@ -3282,7 +3281,7 @@
         <v>400</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>46</v>
@@ -3303,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>49</v>
@@ -3330,10 +3329,10 @@
         <v>280</v>
       </c>
       <c r="AG20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AH20" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="AH20" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="AI20" s="1">
         <v>2.2000000000000002</v>
@@ -3341,10 +3340,10 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>74</v>
@@ -3356,13 +3355,13 @@
         <v>110</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>30</v>
@@ -3389,7 +3388,7 @@
         <v>500</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>46</v>
@@ -3410,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y21" s="1" t="s">
         <v>71</v>
@@ -3428,7 +3427,7 @@
         <v>2</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE21" s="1">
         <v>80</v>
@@ -3437,7 +3436,7 @@
         <v>280</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AH21" s="1">
         <v>24.8</v>
@@ -3448,13 +3447,13 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="D22" s="1">
         <v>115</v>
@@ -3496,10 +3495,10 @@
         <v>500</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>30</v>
@@ -3535,7 +3534,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AE22" s="1">
         <v>80</v>
@@ -3544,10 +3543,10 @@
         <v>245</v>
       </c>
       <c r="AG22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH22" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="AH22" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="AI22" s="1">
         <v>2.4</v>
@@ -3555,13 +3554,13 @@
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
@@ -3603,10 +3602,10 @@
         <v>500</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>30</v>
@@ -3624,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Z23" s="1" t="s">
         <v>30</v>
@@ -3642,7 +3641,7 @@
         <v>2</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE23" s="1">
         <v>80</v>
@@ -3651,7 +3650,7 @@
         <v>240</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AH23" s="1">
         <v>26.9</v>
@@ -3662,13 +3661,13 @@
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D24" s="1">
         <v>200</v>
@@ -3677,7 +3676,7 @@
         <v>130</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>59</v>
@@ -3710,10 +3709,10 @@
         <v>500</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>30</v>
@@ -3731,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y24" s="1" t="s">
         <v>71</v>
@@ -3749,7 +3748,7 @@
         <v>2</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE24" s="1">
         <v>60</v>
@@ -3758,7 +3757,7 @@
         <v>250</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AH24" s="1">
         <v>20</v>
@@ -3769,13 +3768,13 @@
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D25" s="1">
         <v>195</v>
@@ -3817,7 +3816,7 @@
         <v>500</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>46</v>
@@ -3856,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AE25" s="1">
         <v>80</v>
@@ -3865,10 +3864,10 @@
         <v>245</v>
       </c>
       <c r="AG25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH25" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="AH25" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="AI25" s="1">
         <v>2.4</v>
@@ -3876,13 +3875,13 @@
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D26" s="1">
         <v>80</v>
@@ -3924,10 +3923,10 @@
         <v>500</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>30</v>
@@ -3948,7 +3947,7 @@
         <v>31</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z26" s="1" t="s">
         <v>30</v>
@@ -3972,10 +3971,10 @@
         <v>230</v>
       </c>
       <c r="AG26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH26" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="AH26" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="AI26" s="1">
         <v>2.4</v>
@@ -3983,13 +3982,13 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D27" s="1">
         <v>168</v>
@@ -4031,7 +4030,7 @@
         <v>400</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>46</v>
@@ -4052,7 +4051,7 @@
         <v>1</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y27" s="1" t="s">
         <v>71</v>
@@ -4070,7 +4069,7 @@
         <v>2</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AE27" s="1">
         <v>60</v>
@@ -4079,10 +4078,10 @@
         <v>245</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI27" s="1">
         <v>2.1</v>
@@ -4090,13 +4089,13 @@
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D28" s="1">
         <v>115</v>
@@ -4138,10 +4137,10 @@
         <v>500</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>30</v>
@@ -4177,7 +4176,7 @@
         <v>4</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AE28" s="1">
         <v>80</v>
@@ -4186,10 +4185,10 @@
         <v>300</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AI28" s="1">
         <v>2.56</v>
@@ -4197,13 +4196,13 @@
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D29" s="1">
         <v>130</v>
@@ -4245,7 +4244,7 @@
         <v>500</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>46</v>
@@ -4269,7 +4268,7 @@
         <v>31</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z29" s="1" t="s">
         <v>30</v>
@@ -4293,10 +4292,10 @@
         <v>230</v>
       </c>
       <c r="AG29" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH29" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="AH29" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="AI29" s="1">
         <v>2.4</v>
@@ -4304,13 +4303,13 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D30" s="1">
         <v>110</v>
@@ -4340,7 +4339,7 @@
         <v>16</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>26</v>
@@ -4352,7 +4351,7 @@
         <v>1200</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>46</v>
@@ -4411,13 +4410,13 @@
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D31" s="1">
         <v>90</v>
@@ -4462,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>30</v>
@@ -4548,7 +4547,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4560,45 +4559,45 @@
         <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
@@ -4648,7 +4647,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>41</v>
@@ -4698,7 +4697,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>41</v>
@@ -4736,7 +4735,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>41</v>
@@ -4774,10 +4773,10 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>58</v>
@@ -4812,10 +4811,10 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>63</v>
@@ -4850,7 +4849,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>65</v>
@@ -4888,7 +4887,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>69</v>
@@ -4926,7 +4925,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>70</v>
@@ -4966,10 +4965,10 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>63</v>
@@ -4986,7 +4985,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>70</v>
@@ -5006,7 +5005,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>74</v>
@@ -5026,10 +5025,10 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>58</v>
@@ -5046,10 +5045,10 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>58</v>
@@ -5066,7 +5065,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>70</v>
@@ -5086,16 +5085,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E18" s="1">
         <v>2095</v>
@@ -5106,7 +5105,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>65</v>
@@ -5115,7 +5114,7 @@
         <v>63</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E19" s="1">
         <v>1756</v>
@@ -5126,7 +5125,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>70</v>
@@ -5146,16 +5145,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E21" s="1">
         <v>2126</v>
@@ -5166,10 +5165,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>63</v>
@@ -5186,10 +5185,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>63</v>
@@ -5206,13 +5205,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>37</v>
@@ -5226,10 +5225,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>63</v>
@@ -5246,10 +5245,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>63</v>
@@ -5266,10 +5265,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>63</v>
@@ -5286,10 +5285,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>63</v>
@@ -5306,10 +5305,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>58</v>
@@ -5326,10 +5325,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>42</v>
@@ -5352,10 +5351,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>58</v>
@@ -5395,7 +5394,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -5407,24 +5406,24 @@
         <v>36</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
@@ -5453,7 +5452,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>41</v>
@@ -5482,7 +5481,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>41</v>
@@ -5511,16 +5510,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="E5" s="5">
         <v>43405</v>
@@ -5540,7 +5539,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>41</v>
@@ -5569,10 +5568,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>58</v>
@@ -5598,10 +5597,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>63</v>
@@ -5627,7 +5626,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>65</v>
@@ -5656,7 +5655,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>69</v>
@@ -5685,7 +5684,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>70</v>
@@ -5719,10 +5718,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>63</v>
@@ -5736,7 +5735,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>70</v>
@@ -5753,7 +5752,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>74</v>
@@ -5770,10 +5769,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>58</v>
@@ -5787,10 +5786,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>58</v>
@@ -5804,7 +5803,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>70</v>
@@ -5821,16 +5820,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3">
         <v>17579</v>
@@ -5838,7 +5837,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>65</v>
@@ -5847,7 +5846,7 @@
         <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3">
         <v>12320</v>
@@ -5855,7 +5854,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>70</v>
@@ -5872,16 +5871,16 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3">
         <v>17652</v>
@@ -5889,10 +5888,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>63</v>
@@ -5906,10 +5905,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>63</v>
@@ -5923,13 +5922,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>37</v>
@@ -5940,10 +5939,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>63</v>
@@ -5957,10 +5956,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>63</v>
@@ -5974,10 +5973,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>63</v>
@@ -5991,10 +5990,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>63</v>
@@ -6008,10 +6007,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>58</v>
@@ -6025,10 +6024,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>42</v>
@@ -6042,10 +6041,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>58</v>
@@ -6087,7 +6086,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -6099,39 +6098,39 @@
         <v>36</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>23</v>
@@ -6145,7 +6144,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>41</v>
@@ -6189,7 +6188,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>41</v>
@@ -6233,7 +6232,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>41</v>
@@ -6277,10 +6276,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>58</v>
@@ -6321,10 +6320,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>63</v>
@@ -6335,7 +6334,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>65</v>
@@ -6349,7 +6348,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>69</v>
@@ -6363,7 +6362,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>70</v>
@@ -6400,10 +6399,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>63</v>
@@ -6420,7 +6419,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>70</v>
@@ -6440,7 +6439,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>74</v>
@@ -6460,10 +6459,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>58</v>
@@ -6480,10 +6479,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>58</v>
@@ -6500,7 +6499,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>70</v>
@@ -6520,16 +6519,16 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F18" s="6">
         <v>119</v>
@@ -6540,7 +6539,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>65</v>
@@ -6549,7 +6548,7 @@
         <v>63</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F19" s="6">
         <v>60</v>
@@ -6560,7 +6559,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>70</v>
@@ -6580,16 +6579,16 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F21" s="6">
         <v>129</v>
@@ -6600,10 +6599,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>63</v>
@@ -6620,10 +6619,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>63</v>
@@ -6640,13 +6639,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>37</v>
@@ -6660,10 +6659,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>63</v>
@@ -6677,10 +6676,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>63</v>
@@ -6694,10 +6693,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>63</v>
@@ -6714,10 +6713,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>63</v>
@@ -6734,10 +6733,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>58</v>
@@ -6754,10 +6753,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>42</v>
@@ -6774,10 +6773,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>58</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\page\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADC5BD0-91B4-49F0-854E-D535415F0BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61825B0E-1002-4FC1-85D7-3F3742B06E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="207">
   <si>
     <t>CPU</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -729,6 +729,51 @@
   </si>
   <si>
     <t>Silicon Brand</t>
+  </si>
+  <si>
+    <t>MECHREVO 蒼龍16 Ultra</t>
+  </si>
+  <si>
+    <t>MECHREVO 蛟龙16Pro</t>
+  </si>
+  <si>
+    <t>258.9x257.3</t>
+  </si>
+  <si>
+    <t>HP 星bookpro16</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>X7 358H</t>
+  </si>
+  <si>
+    <t>B390</t>
+  </si>
+  <si>
+    <t>LPDDR5x 8533MHz</t>
+  </si>
+  <si>
+    <t>15.05-19.9</t>
+  </si>
+  <si>
+    <t>357.8x54.85</t>
+  </si>
+  <si>
+    <t>2C1A</t>
+  </si>
+  <si>
+    <t>TUF A14 FA401EA</t>
+  </si>
+  <si>
+    <t>AI MAX+ 392</t>
+  </si>
+  <si>
+    <t>8060S</t>
+  </si>
+  <si>
+    <t>LPDDR5x 8000MHz</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5317B7F1-97B1-4158-9079-381F44477F99}">
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -4303,7 +4348,7 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>64</v>
@@ -4513,6 +4558,327 @@
       </c>
       <c r="AI31" s="1">
         <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="1">
+        <v>140</v>
+      </c>
+      <c r="E32" s="1">
+        <v>110</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K32" s="1">
+        <v>205</v>
+      </c>
+      <c r="L32" s="1">
+        <v>16</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O32" s="1">
+        <v>300</v>
+      </c>
+      <c r="P32" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T32" s="1">
+        <v>2</v>
+      </c>
+      <c r="U32" s="1">
+        <v>2</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W32" s="1">
+        <v>1</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB32" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>80</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>280</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AH32" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="AI32" s="1">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" s="1">
+        <v>80</v>
+      </c>
+      <c r="E33" s="1">
+        <v>65</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K33" s="1">
+        <v>60</v>
+      </c>
+      <c r="L33" s="1">
+        <v>16</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" s="1">
+        <v>240</v>
+      </c>
+      <c r="P33" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U33" s="1">
+        <v>2</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>67</v>
+      </c>
+      <c r="AF33" s="1">
+        <v>100</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH33" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI33" s="1">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" s="1">
+        <v>115</v>
+      </c>
+      <c r="E34" s="1">
+        <v>85</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K34" s="1">
+        <v>85</v>
+      </c>
+      <c r="L34" s="1">
+        <v>14</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O34" s="1">
+        <v>165</v>
+      </c>
+      <c r="P34" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U34" s="1">
+        <v>2</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>76</v>
+      </c>
+      <c r="AF34" s="1">
+        <v>200</v>
+      </c>
+      <c r="AG34" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH34" s="1">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AI34" s="1">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>
@@ -4524,7 +4890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFEAC08-C68E-4DC7-8960-5E0970DAA788}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -5369,6 +5735,78 @@
         <v>29484</v>
       </c>
     </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1861</v>
+      </c>
+      <c r="G32" s="1">
+        <v>26151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2085</v>
+      </c>
+      <c r="G33" s="1">
+        <v>19787</v>
+      </c>
+      <c r="H33" s="1">
+        <v>121</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1965</v>
+      </c>
+      <c r="G34" s="1">
+        <v>26131</v>
+      </c>
+      <c r="H34" s="1">
+        <v>112</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1416</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5377,7 +5815,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAE2845-E5DA-4A2F-AF36-B0EED8E1A7B7}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="7.1796875" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -6056,6 +6494,57 @@
         <v>14546</v>
       </c>
     </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" s="3">
+        <v>17521</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="3">
+        <v>7021</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="3">
+        <v>11035</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6064,11 +6553,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0621FDEC-049F-42F4-9153-BBF6657B44B9}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="20.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.90625" style="6" bestFit="1" customWidth="1"/>
@@ -6791,6 +7280,66 @@
         <v>120</v>
       </c>
     </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F32" s="6">
+        <v>113</v>
+      </c>
+      <c r="H32" s="6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="6">
+        <v>47</v>
+      </c>
+      <c r="H33" s="6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" s="6">
+        <v>75</v>
+      </c>
+      <c r="H34" s="6">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\page\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\X16\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61825B0E-1002-4FC1-85D7-3F3742B06E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{368C9534-2790-4965-9A6C-E937D51AD0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
+    <workbookView xWindow="-38510" yWindow="-5610" windowWidth="38620" windowHeight="21100" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="221">
   <si>
     <t>CPU</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -774,6 +774,62 @@
   </si>
   <si>
     <t>LPDDR5x 8000MHz</t>
+  </si>
+  <si>
+    <t>U9 185H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Port Royal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R26 [1T]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R26 [nT] 1 run</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R26 [nT] 10 mins</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GBT Aero X16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 9 HX 470</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solar Bay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Steel Nomad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 9 465</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDDR7 12GB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1*G4x4 1*G4x2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>355x250.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.75~19.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -781,28 +837,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="165" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -810,13 +866,13 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Aptos Narrow"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -850,7 +906,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -862,7 +918,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1202,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5317B7F1-97B1-4158-9079-381F44477F99}">
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -4881,6 +4937,315 @@
         <v>1.48</v>
       </c>
     </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D35" s="1">
+        <v>82</v>
+      </c>
+      <c r="E35" s="1">
+        <v>70</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="1">
+        <v>135</v>
+      </c>
+      <c r="L35" s="1">
+        <v>16</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" s="1">
+        <v>165</v>
+      </c>
+      <c r="P35" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T35" s="1">
+        <v>2</v>
+      </c>
+      <c r="U35" s="1">
+        <v>2</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W35" s="1">
+        <v>1</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB35" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC35" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>76</v>
+      </c>
+      <c r="AF35" s="1">
+        <v>240</v>
+      </c>
+      <c r="AG35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI35" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>16</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O36" s="1">
+        <v>165</v>
+      </c>
+      <c r="P36" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T36" s="1">
+        <v>2</v>
+      </c>
+      <c r="U36" s="1">
+        <v>2</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="W36" s="1">
+        <v>1</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>76</v>
+      </c>
+      <c r="AF36" s="1">
+        <v>150</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AH36" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AI36" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>16</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O37" s="1">
+        <v>165</v>
+      </c>
+      <c r="P37" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T37" s="1">
+        <v>2</v>
+      </c>
+      <c r="U37" s="1">
+        <v>2</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="W37" s="1">
+        <v>1</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC37" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>76</v>
+      </c>
+      <c r="AF37" s="1">
+        <v>150</v>
+      </c>
+      <c r="AG37" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AH37" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AI37" s="1">
+        <v>1.9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4890,7 +5255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFEAC08-C68E-4DC7-8960-5E0970DAA788}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -4903,15 +5268,16 @@
     <col min="8" max="8" width="8.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.7265625" style="1"/>
+    <col min="11" max="13" width="16.453125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="34.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,25 +5309,34 @@
         <v>93</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -4992,26 +5367,29 @@
       <c r="J2" s="2">
         <v>755</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2">
         <v>66.599999999999994</v>
       </c>
-      <c r="L2" s="2">
+      <c r="O2" s="2">
         <v>39.799999999999997</v>
       </c>
-      <c r="M2" s="1">
+      <c r="P2" s="1">
         <v>8436</v>
       </c>
-      <c r="N2" s="1">
+      <c r="Q2" s="1">
         <v>9366</v>
       </c>
-      <c r="O2" s="1">
+      <c r="R2" s="1">
         <v>14214</v>
       </c>
-      <c r="P2" s="1">
+      <c r="S2" s="1">
         <v>12241</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -5042,26 +5420,29 @@
       <c r="J3" s="2">
         <v>2057</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2">
         <v>119.6</v>
       </c>
-      <c r="L3" s="2">
+      <c r="O3" s="2">
         <v>104.6</v>
       </c>
-      <c r="M3" s="1">
+      <c r="P3" s="1">
         <v>10385</v>
       </c>
-      <c r="N3" s="1">
+      <c r="Q3" s="1">
         <v>10699</v>
       </c>
-      <c r="O3" s="1">
+      <c r="R3" s="1">
         <v>15056</v>
       </c>
-      <c r="P3" s="1">
+      <c r="S3" s="1">
         <v>18867</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>83</v>
       </c>
@@ -5092,14 +5473,17 @@
       <c r="J4" s="2">
         <v>2015</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="1">
         <v>117</v>
       </c>
-      <c r="L4" s="1">
+      <c r="O4" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>84</v>
       </c>
@@ -5130,14 +5514,17 @@
       <c r="J5" s="2">
         <v>2057</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="1">
         <v>117</v>
       </c>
-      <c r="L5" s="1">
+      <c r="O5" s="1">
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
@@ -5168,14 +5555,17 @@
       <c r="J6" s="2">
         <v>779</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
         <v>71.900000000000006</v>
       </c>
-      <c r="L6" s="2">
+      <c r="O6" s="2">
         <v>44.7</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>85</v>
       </c>
@@ -5206,14 +5596,17 @@
       <c r="J7" s="2">
         <v>820</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
         <v>70</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>43.8</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>86</v>
       </c>
@@ -5244,14 +5637,17 @@
       <c r="J8" s="2">
         <v>928</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2">
         <v>76.2</v>
       </c>
-      <c r="L8" s="2">
+      <c r="O8" s="2">
         <v>56.4</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>86</v>
       </c>
@@ -5282,14 +5678,17 @@
       <c r="J9" s="2">
         <v>724</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2">
         <v>67.2</v>
       </c>
-      <c r="L9" s="2">
+      <c r="O9" s="2">
         <v>47.2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
@@ -5309,7 +5708,7 @@
         <v>31375</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>75</v>
       </c>
@@ -5329,7 +5728,7 @@
         <v>35477</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>182</v>
       </c>
@@ -5349,7 +5748,7 @@
         <v>18607</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>154</v>
       </c>
@@ -5369,7 +5768,7 @@
         <v>32647</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>125</v>
       </c>
@@ -5389,7 +5788,7 @@
         <v>38641</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>183</v>
       </c>
@@ -5409,7 +5808,7 @@
         <v>25970</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>133</v>
       </c>
@@ -5755,7 +6154,7 @@
         <v>26151</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>195</v>
       </c>
@@ -5781,7 +6180,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>203</v>
       </c>
@@ -5805,6 +6204,183 @@
       </c>
       <c r="I34" s="1">
         <v>1416</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1883</v>
+      </c>
+      <c r="F35" s="1">
+        <v>19145</v>
+      </c>
+      <c r="G35" s="1">
+        <v>18152</v>
+      </c>
+      <c r="H35" s="1">
+        <v>114</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1015</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1020</v>
+      </c>
+      <c r="K35" s="1">
+        <v>459</v>
+      </c>
+      <c r="L35" s="1">
+        <v>4268</v>
+      </c>
+      <c r="M35" s="1">
+        <v>4245</v>
+      </c>
+      <c r="N35" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="O35" s="1">
+        <v>55.5</v>
+      </c>
+      <c r="P35" s="1">
+        <v>9390</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>10265</v>
+      </c>
+      <c r="R35" s="1">
+        <v>16150</v>
+      </c>
+      <c r="S35" s="1">
+        <v>13553</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2065</v>
+      </c>
+      <c r="F36" s="1">
+        <v>24113</v>
+      </c>
+      <c r="G36" s="1">
+        <v>18384</v>
+      </c>
+      <c r="H36" s="1">
+        <v>120</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1153</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1180</v>
+      </c>
+      <c r="K36" s="1">
+        <v>492</v>
+      </c>
+      <c r="L36" s="1">
+        <v>5084</v>
+      </c>
+      <c r="M36" s="1">
+        <v>5079</v>
+      </c>
+      <c r="N36" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="O36" s="1">
+        <v>73.8</v>
+      </c>
+      <c r="P36" s="1">
+        <v>10109</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>10701</v>
+      </c>
+      <c r="R36" s="1">
+        <v>18252</v>
+      </c>
+      <c r="S36" s="1">
+        <v>14142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1993</v>
+      </c>
+      <c r="F37" s="1">
+        <v>20907</v>
+      </c>
+      <c r="G37" s="1">
+        <v>20687</v>
+      </c>
+      <c r="H37" s="1">
+        <v>116</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1092</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1076</v>
+      </c>
+      <c r="K37" s="1">
+        <v>478</v>
+      </c>
+      <c r="L37" s="1">
+        <v>4413</v>
+      </c>
+      <c r="M37" s="1">
+        <v>4479</v>
+      </c>
+      <c r="N37" s="1">
+        <v>77.5</v>
+      </c>
+      <c r="O37" s="1">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="P37" s="1">
+        <v>9311</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>10459</v>
+      </c>
+      <c r="R37" s="1">
+        <v>14832</v>
+      </c>
+      <c r="S37" s="1">
+        <v>14121</v>
       </c>
     </row>
   </sheetData>
@@ -5815,7 +6391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAE2845-E5DA-4A2F-AF36-B0EED8E1A7B7}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="7.1796875" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -5827,10 +6403,13 @@
     <col min="7" max="7" width="21.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="7.1796875" style="3"/>
+    <col min="10" max="10" width="10.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="7.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
@@ -5858,8 +6437,17 @@
       <c r="I1" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J1" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -5888,7 +6476,7 @@
         <v>8041</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -5917,7 +6505,7 @@
         <v>11769</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>83</v>
       </c>
@@ -5946,7 +6534,7 @@
         <v>10614</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
@@ -5975,7 +6563,7 @@
         <v>8362</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>84</v>
       </c>
@@ -6004,7 +6592,7 @@
         <v>6513</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>85</v>
       </c>
@@ -6033,7 +6621,7 @@
         <v>5690</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>85</v>
       </c>
@@ -6062,7 +6650,7 @@
         <v>5084</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>86</v>
       </c>
@@ -6091,7 +6679,7 @@
         <v>5048</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>86</v>
       </c>
@@ -6120,7 +6708,7 @@
         <v>4383</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>87</v>
       </c>
@@ -6137,7 +6725,7 @@
         <v>12657</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -6154,7 +6742,7 @@
         <v>13957</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>182</v>
       </c>
@@ -6171,7 +6759,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>154</v>
       </c>
@@ -6188,7 +6776,7 @@
         <v>13797</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>125</v>
       </c>
@@ -6205,7 +6793,7 @@
         <v>14262</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>183</v>
       </c>
@@ -6494,7 +7082,7 @@
         <v>14546</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="7" t="s">
         <v>193</v>
       </c>
@@ -6511,7 +7099,7 @@
         <v>17521</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>195</v>
       </c>
@@ -6528,7 +7116,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>203</v>
       </c>
@@ -6543,6 +7131,114 @@
       </c>
       <c r="H35" s="3">
         <v>11035</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="3">
+        <v>35406</v>
+      </c>
+      <c r="F36" s="3">
+        <v>16970</v>
+      </c>
+      <c r="G36" s="3">
+        <v>7898</v>
+      </c>
+      <c r="H36" s="3">
+        <v>13410</v>
+      </c>
+      <c r="I36" s="3">
+        <v>6195</v>
+      </c>
+      <c r="J36" s="3">
+        <v>8502</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="3">
+        <v>30798</v>
+      </c>
+      <c r="F37" s="3">
+        <v>14396</v>
+      </c>
+      <c r="G37" s="3">
+        <v>6709</v>
+      </c>
+      <c r="H37" s="3">
+        <v>11096</v>
+      </c>
+      <c r="I37" s="3">
+        <v>5228</v>
+      </c>
+      <c r="J37" s="3">
+        <v>6976</v>
+      </c>
+      <c r="K37" s="3">
+        <v>51090</v>
+      </c>
+      <c r="L37" s="3">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="3">
+        <v>34899</v>
+      </c>
+      <c r="F38" s="3">
+        <v>16534</v>
+      </c>
+      <c r="G38" s="3">
+        <v>7579</v>
+      </c>
+      <c r="H38" s="3">
+        <v>12939</v>
+      </c>
+      <c r="I38" s="3">
+        <v>5972</v>
+      </c>
+      <c r="J38" s="3">
+        <v>8324</v>
+      </c>
+      <c r="K38" s="3">
+        <v>58825</v>
+      </c>
+      <c r="L38" s="3">
+        <v>2810</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\X16\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{368C9534-2790-4965-9A6C-E937D51AD0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6300B9-52FD-4F61-A4D0-A78333F50F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-5610" windowWidth="38620" windowHeight="21100" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
+    <workbookView xWindow="-38510" yWindow="-5610" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="228">
   <si>
     <t>CPU</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -829,6 +829,34 @@
   </si>
   <si>
     <t>16.75~19.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GBT Eagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R5 7533HS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTX4050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDDR6 6GB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDR5 4800MHz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.59~23.99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1258,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5317B7F1-97B1-4158-9079-381F44477F99}">
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI38"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -5246,6 +5274,107 @@
         <v>1.9</v>
       </c>
     </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="1">
+        <v>80</v>
+      </c>
+      <c r="L38" s="1">
+        <v>16</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" s="1">
+        <v>165</v>
+      </c>
+      <c r="P38" s="1">
+        <v>400</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T38" s="1">
+        <v>2</v>
+      </c>
+      <c r="U38" s="1">
+        <v>2</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W38" s="1">
+        <v>1</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>61</v>
+      </c>
+      <c r="AF38" s="1">
+        <v>135</v>
+      </c>
+      <c r="AG38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH38" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="AI38" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5255,7 +5384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFEAC08-C68E-4DC7-8960-5E0970DAA788}">
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -6383,6 +6512,65 @@
         <v>14121</v>
       </c>
     </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1446</v>
+      </c>
+      <c r="F38" s="1">
+        <v>10783</v>
+      </c>
+      <c r="G38" s="1">
+        <v>10508</v>
+      </c>
+      <c r="H38" s="1">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1">
+        <v>600</v>
+      </c>
+      <c r="J38" s="1">
+        <v>595</v>
+      </c>
+      <c r="K38" s="1">
+        <v>348</v>
+      </c>
+      <c r="L38" s="1">
+        <v>2239</v>
+      </c>
+      <c r="M38" s="1">
+        <v>2379</v>
+      </c>
+      <c r="N38" s="1">
+        <v>54.1</v>
+      </c>
+      <c r="O38" s="1">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="P38" s="1">
+        <v>7529</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>9805</v>
+      </c>
+      <c r="R38" s="1">
+        <v>11889</v>
+      </c>
+      <c r="S38" s="1">
+        <v>9934</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6391,7 +6579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAE2845-E5DA-4A2F-AF36-B0EED8E1A7B7}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultColWidth="7.1796875" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -7239,6 +7427,38 @@
       </c>
       <c r="L38" s="3">
         <v>2810</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E39" s="3">
+        <v>21511</v>
+      </c>
+      <c r="F39" s="3">
+        <v>9596</v>
+      </c>
+      <c r="G39" s="3">
+        <v>4191</v>
+      </c>
+      <c r="H39" s="3">
+        <v>7750</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3551</v>
+      </c>
+      <c r="J39" s="3">
+        <v>4398</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6300B9-52FD-4F61-A4D0-A78333F50F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-5610" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
+    <workbookView xWindow="-38510" yWindow="-5610" windowWidth="38620" windowHeight="21100" xr2:uid="{5912F292-AF02-443D-9037-F31B49618F6B}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="4" r:id="rId1"/>
